--- a/document/タスク一覧表示画面_画面設計書.xlsx
+++ b/document/タスク一覧表示画面_画面設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E21E48-CF46-4A98-BA32-BE5D58968D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44387AE9-3605-4DBC-BD51-878981539D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="116">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -517,6 +517,34 @@
     <t>POST</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>⑤</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へボタン</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面に戻る</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1431,6 +1459,9 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1449,6 +1480,141 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1458,12 +1624,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1473,123 +1633,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1614,91 +1657,115 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1707,53 +1774,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2059,16 +2087,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>593912</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>134471</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>235323</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>448235</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>235324</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33617</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2083,7 +2111,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="9603441" y="1658471"/>
+          <a:off x="10354235" y="2364441"/>
           <a:ext cx="963706" cy="369794"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2109,16 +2137,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>392206</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>168089</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>537883</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>257736</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>290604</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>436281</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2160,7 +2188,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10511118" y="1423148"/>
+          <a:off x="11239501" y="2050677"/>
           <a:ext cx="481104" cy="470646"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2682,6 +2710,247 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>806823</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>201705</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A4CBD2-9611-4C98-9771-EA9811F30712}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7597588" y="1669676"/>
+          <a:ext cx="1792941" cy="324970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+            <a:t>メニュー画面へ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>694765</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>582707</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>246530</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D92ECE-FC5F-4B77-8C5E-0643C822608F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7485530" y="1624853"/>
+          <a:ext cx="2106706" cy="414618"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>560295</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>414618</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{150702D7-C557-4618-B74E-A18D281B5E52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="9569824" y="1434353"/>
+          <a:ext cx="963706" cy="369794"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>324970</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>280147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>246528</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="グラフィックス 16" descr="バッジ 5 枠線">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A338472-6D76-69DE-3E76-4658273D9ABD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10443882" y="1176618"/>
+          <a:ext cx="504264" cy="504264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2892,85 +3161,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="104"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="107"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="107"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2990,46 +3259,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="98" t="s">
+      <c r="G13" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="100"/>
-      <c r="I13" s="98" t="s">
+      <c r="H13" s="105"/>
+      <c r="I13" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="99"/>
-      <c r="K13" s="100"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="105"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="98"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="100"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="105"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="98"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="100"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="105"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3038,13 +3307,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="101" t="s">
+      <c r="G17" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="102"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4058,19 +4327,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="122"/>
+      <c r="G1" s="111"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4082,168 +4351,168 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="82"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="130"/>
+      <c r="A3" s="130"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="119"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="139"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="110"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="123"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="110"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="123"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="110"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="123"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="110"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="123"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="125"/>
-      <c r="B10" s="127" t="s">
+      <c r="A10" s="136"/>
+      <c r="B10" s="121" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="100"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="110"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="123"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127" t="s">
+      <c r="A11" s="137"/>
+      <c r="B11" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="110"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="123"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="123" t="s">
+      <c r="A12" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="110"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="123"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="107"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="138"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5234,17 +5503,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5253,14 +5519,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5279,19 +5548,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="122"/>
+      <c r="G1" s="111"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5303,40 +5572,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="82"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="130"/>
+      <c r="A3" s="130"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="119"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6692,19 +6961,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="122"/>
+      <c r="G1" s="111"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6716,40 +6985,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="82"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="130"/>
+      <c r="A3" s="130"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="119"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8094,7 +8363,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="6.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
     <col min="7" max="7" width="27.42578125" customWidth="1"/>
@@ -8103,19 +8372,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8127,112 +8396,112 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="54"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="59"/>
+      <c r="F2" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="76">
+      <c r="G2" s="59"/>
+      <c r="H2" s="64">
         <v>46177</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="82"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="54"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="83"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="95" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="97"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="91"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="54"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="56"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="40"/>
       <c r="B9" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="57"/>
+      <c r="D9" s="101"/>
       <c r="E9" s="43" t="s">
         <v>80</v>
       </c>
@@ -8245,20 +8514,20 @@
       <c r="H9" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="40"/>
       <c r="B10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="77"/>
       <c r="E10" s="3" t="s">
         <v>86</v>
       </c>
@@ -8271,20 +8540,20 @@
       <c r="H10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="56"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="40"/>
       <c r="B11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="55"/>
+      <c r="D11" s="77"/>
       <c r="E11" s="3" t="s">
         <v>85</v>
       </c>
@@ -8297,92 +8566,92 @@
       <c r="H11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="55" t="s">
+      <c r="I11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="56"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="40"/>
       <c r="B12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="40"/>
       <c r="B13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="40"/>
       <c r="B14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="56"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="100"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="41"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
       <c r="E15" s="42"/>
       <c r="F15" s="42"/>
       <c r="G15" s="42"/>
       <c r="H15" s="42"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="100"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="67"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="91"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="150" t="s">
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="152"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="95"/>
       <c r="I17" s="15" t="s">
         <v>27</v>
       </c>
@@ -8391,11 +8660,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="68"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="15" t="s">
         <v>29</v>
       </c>
@@ -8408,18 +8677,18 @@
       <c r="G18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="66"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="91"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="17" t="s">
         <v>96</v>
       </c>
@@ -8429,21 +8698,21 @@
       <c r="F19" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="148" t="s">
+      <c r="G19" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="149" t="s">
+      <c r="H19" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="49"/>
-      <c r="J19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="17" t="s">
         <v>99</v>
       </c>
@@ -8453,21 +8722,21 @@
       <c r="F20" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="148" t="s">
+      <c r="G20" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="48" t="s">
+      <c r="H20" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="17" t="s">
         <v>100</v>
       </c>
@@ -8480,18 +8749,18 @@
       <c r="G21" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="48" t="s">
+      <c r="H21" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="49"/>
-      <c r="J21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="17" t="s">
         <v>101</v>
       </c>
@@ -8504,35 +8773,47 @@
       <c r="G22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="48" t="s">
+      <c r="H22" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="49"/>
-      <c r="J22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
+      <c r="A23" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23" s="50"/>
+      <c r="J23" s="51"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="70"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="72"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="54"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="20"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="75"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9513,6 +9794,33 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -9529,33 +9837,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9575,182 +9856,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="127" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="93" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="93" t="s">
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="93" t="s">
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="93" t="s">
+      <c r="P1" s="111"/>
+      <c r="Q1" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="122"/>
-      <c r="S1" s="93" t="s">
+      <c r="R1" s="111"/>
+      <c r="S1" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="109"/>
+      <c r="T1" s="139"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="144"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="145"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="133"/>
-      <c r="T3" s="145"/>
+      <c r="A3" s="130"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="146"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="120"/>
-      <c r="S4" s="134"/>
-      <c r="T4" s="146"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="132"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="116"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="147"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="95" t="s">
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="109"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="139"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="48" t="s">
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="99"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="110"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="104"/>
+      <c r="T6" s="123"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="48" t="s">
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="110"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
+      <c r="S7" s="104"/>
+      <c r="T7" s="123"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9949,37 +10230,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="100"/>
-      <c r="C15" s="142" t="s">
+      <c r="B15" s="105"/>
+      <c r="C15" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="100"/>
-      <c r="E15" s="69" t="s">
+      <c r="D15" s="105"/>
+      <c r="E15" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="100"/>
-      <c r="G15" s="69" t="s">
+      <c r="F15" s="105"/>
+      <c r="G15" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="99"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="69" t="s">
+      <c r="H15" s="104"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="100"/>
-      <c r="L15" s="69" t="s">
+      <c r="K15" s="105"/>
+      <c r="L15" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="99"/>
-      <c r="N15" s="100"/>
-      <c r="O15" s="69" t="s">
+      <c r="M15" s="104"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
+      <c r="P15" s="104"/>
+      <c r="Q15" s="105"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9991,37 +10272,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="135">
+      <c r="A16" s="148">
         <v>1</v>
       </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="136" t="s">
+      <c r="B16" s="105"/>
+      <c r="C16" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="100"/>
-      <c r="E16" s="136" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="100"/>
-      <c r="G16" s="141" t="s">
+      <c r="F16" s="105"/>
+      <c r="G16" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="99"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="141" t="s">
+      <c r="H16" s="104"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="100"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="105"/>
+      <c r="L16" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="99"/>
-      <c r="N16" s="100"/>
-      <c r="O16" s="139" t="s">
+      <c r="M16" s="104"/>
+      <c r="N16" s="105"/>
+      <c r="O16" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="100"/>
+      <c r="P16" s="104"/>
+      <c r="Q16" s="105"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -10033,37 +10314,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="135">
+      <c r="A17" s="148">
         <v>2</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="136" t="s">
+      <c r="B17" s="105"/>
+      <c r="C17" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="136" t="s">
+      <c r="D17" s="105"/>
+      <c r="E17" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="100"/>
-      <c r="G17" s="141" t="s">
+      <c r="F17" s="105"/>
+      <c r="G17" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="99"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="141" t="s">
+      <c r="H17" s="104"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="100"/>
-      <c r="L17" s="139" t="s">
+      <c r="K17" s="105"/>
+      <c r="L17" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="99"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="139" t="s">
+      <c r="M17" s="104"/>
+      <c r="N17" s="105"/>
+      <c r="O17" s="142" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="100"/>
+      <c r="P17" s="104"/>
+      <c r="Q17" s="105"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -10075,23 +10356,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="135"/>
-      <c r="B18" s="100"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="100"/>
+      <c r="A18" s="148"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="105"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="105"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -10103,23 +10384,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="135"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="139"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="139"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="100"/>
+      <c r="A19" s="148"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="105"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="105"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -10131,23 +10412,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="100"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="100"/>
+      <c r="A20" s="148"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="105"/>
+      <c r="O20" s="142"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="105"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -10159,23 +10440,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="139"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="100"/>
-      <c r="O21" s="139"/>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="100"/>
+      <c r="A21" s="148"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="142"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="105"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="104"/>
+      <c r="Q21" s="105"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -10187,23 +10468,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="100"/>
-      <c r="O22" s="139"/>
-      <c r="P22" s="99"/>
-      <c r="Q22" s="100"/>
+      <c r="A22" s="148"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="142"/>
+      <c r="P22" s="104"/>
+      <c r="Q22" s="105"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -10215,23 +10496,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="99"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="139"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="100"/>
-      <c r="O23" s="139"/>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="100"/>
+      <c r="A23" s="148"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="142"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="105"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -10243,23 +10524,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="136"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="139"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="139"/>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="100"/>
+      <c r="A24" s="148"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="142"/>
+      <c r="P24" s="104"/>
+      <c r="Q24" s="105"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -10271,23 +10552,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="139"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="100"/>
-      <c r="O25" s="139"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="100"/>
+      <c r="A25" s="148"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="142"/>
+      <c r="P25" s="104"/>
+      <c r="Q25" s="105"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -10299,23 +10580,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="100"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="100"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="105"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="104"/>
+      <c r="Q26" s="105"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -10327,23 +10608,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="139"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="100"/>
+      <c r="A27" s="148"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="105"/>
+      <c r="O27" s="142"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="105"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -10355,23 +10636,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="139"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="100"/>
-      <c r="O28" s="139"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="100"/>
+      <c r="A28" s="148"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="142"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="105"/>
+      <c r="O28" s="142"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="105"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -10383,23 +10664,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="99"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="139"/>
-      <c r="M29" s="99"/>
-      <c r="N29" s="100"/>
-      <c r="O29" s="139"/>
-      <c r="P29" s="99"/>
-      <c r="Q29" s="100"/>
+      <c r="A29" s="148"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="105"/>
+      <c r="O29" s="142"/>
+      <c r="P29" s="104"/>
+      <c r="Q29" s="105"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -10411,23 +10692,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="136"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="139"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="139"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="100"/>
+      <c r="A30" s="148"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="142"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="105"/>
+      <c r="O30" s="142"/>
+      <c r="P30" s="104"/>
+      <c r="Q30" s="105"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -10439,23 +10720,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="106"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="140"/>
-      <c r="P31" s="106"/>
-      <c r="Q31" s="112"/>
+      <c r="A31" s="151"/>
+      <c r="B31" s="126"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="126"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="125"/>
+      <c r="N31" s="126"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="125"/>
+      <c r="Q31" s="126"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11453,62 +11734,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11533,62 +11814,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
